--- a/public/plantilla-semanal-sst.xlsx
+++ b/public/plantilla-semanal-sst.xlsx
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="40">
+  <numFmts count="0"/>
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -301,6 +302,15 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1029,7 +1039,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="376">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1945,6 +1955,47 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2665,16 +2716,16 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="C11" s="364" t="n"/>
+      <c r="D11" s="365" t="n"/>
+      <c r="E11" s="365" t="n"/>
+      <c r="F11" s="365" t="n"/>
+      <c r="G11" s="365" t="n"/>
+      <c r="H11" s="365" t="n"/>
+      <c r="I11" s="365" t="n"/>
+      <c r="J11" s="365" t="n"/>
+      <c r="K11" s="365" t="n"/>
+      <c r="L11" s="366" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2683,20 +2734,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="364" t="n"/>
+      <c r="D12" s="365" t="n"/>
+      <c r="E12" s="365" t="n"/>
+      <c r="F12" s="365" t="n"/>
+      <c r="G12" s="366" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="364" t="n"/>
+      <c r="K12" s="365" t="n"/>
+      <c r="L12" s="366" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2705,24 +2756,24 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="69" t="n"/>
-      <c r="D13" s="89" t="n"/>
+      <c r="C13" s="367" t="n"/>
+      <c r="D13" s="366" t="n"/>
       <c r="E13" s="59" t="inlineStr">
         <is>
           <t>Desde</t>
         </is>
       </c>
       <c r="F13" s="89" t="n"/>
-      <c r="G13" s="69" t="n"/>
-      <c r="H13" s="89" t="n"/>
+      <c r="G13" s="367" t="n"/>
+      <c r="H13" s="366" t="n"/>
       <c r="I13" s="59" t="inlineStr">
         <is>
           <t>Hasta</t>
         </is>
       </c>
       <c r="J13" s="89" t="n"/>
-      <c r="K13" s="69" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="K13" s="367" t="n"/>
+      <c r="L13" s="366" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2731,24 +2782,24 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="69" t="n"/>
-      <c r="D14" s="89" t="n"/>
+      <c r="C14" s="367" t="n"/>
+      <c r="D14" s="366" t="n"/>
       <c r="E14" s="59" t="inlineStr">
         <is>
           <t>Horas-hombre (HHT)</t>
         </is>
       </c>
       <c r="F14" s="89" t="n"/>
-      <c r="G14" s="69" t="n"/>
-      <c r="H14" s="89" t="n"/>
+      <c r="G14" s="367" t="n"/>
+      <c r="H14" s="366" t="n"/>
       <c r="I14" s="59" t="inlineStr">
         <is>
           <t>Días trabajados</t>
         </is>
       </c>
       <c r="J14" s="89" t="n"/>
-      <c r="K14" s="69" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="K14" s="367" t="n"/>
+      <c r="L14" s="366" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="127">
       <c r="A15" s="137" t="inlineStr">
@@ -2807,10 +2858,10 @@
       <c r="L16" s="348" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="127">
-      <c r="A17" s="306" t="n">
+      <c r="A17" s="368" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="230" t="inlineStr">
+      <c r="B17" s="369" t="inlineStr">
         <is>
           <t>Charlas diarias de seguridad</t>
         </is>
@@ -2819,21 +2870,21 @@
       <c r="D17" s="98" t="n"/>
       <c r="E17" s="98" t="n"/>
       <c r="F17" s="97" t="n"/>
-      <c r="G17" s="306" t="n"/>
-      <c r="H17" s="306" t="n"/>
-      <c r="I17" s="360">
+      <c r="G17" s="370" t="n"/>
+      <c r="H17" s="370" t="n"/>
+      <c r="I17" s="371">
         <f>IF(OR(G17="",G17=0,H17=""),"",H17/G17)</f>
         <v/>
       </c>
-      <c r="J17" s="230" t="n"/>
-      <c r="K17" s="98" t="n"/>
-      <c r="L17" s="97" t="n"/>
+      <c r="J17" s="372" t="n"/>
+      <c r="K17" s="373" t="n"/>
+      <c r="L17" s="374" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="127">
-      <c r="A18" s="306" t="n">
+      <c r="A18" s="368" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="230" t="inlineStr">
+      <c r="B18" s="369" t="inlineStr">
         <is>
           <t>Inducciones SST</t>
         </is>
@@ -2842,21 +2893,21 @@
       <c r="D18" s="98" t="n"/>
       <c r="E18" s="98" t="n"/>
       <c r="F18" s="97" t="n"/>
-      <c r="G18" s="306" t="n"/>
-      <c r="H18" s="306" t="n"/>
-      <c r="I18" s="360">
+      <c r="G18" s="370" t="n"/>
+      <c r="H18" s="370" t="n"/>
+      <c r="I18" s="371">
         <f>IF(OR(G18="",G18=0,H18=""),"",H18/G18)</f>
         <v/>
       </c>
-      <c r="J18" s="230" t="n"/>
-      <c r="K18" s="98" t="n"/>
-      <c r="L18" s="97" t="n"/>
+      <c r="J18" s="372" t="n"/>
+      <c r="K18" s="373" t="n"/>
+      <c r="L18" s="374" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="127">
-      <c r="A19" s="306" t="n">
+      <c r="A19" s="368" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="230" t="inlineStr">
+      <c r="B19" s="369" t="inlineStr">
         <is>
           <t>Capacitaciones y entrenamientos</t>
         </is>
@@ -2865,21 +2916,21 @@
       <c r="D19" s="98" t="n"/>
       <c r="E19" s="98" t="n"/>
       <c r="F19" s="97" t="n"/>
-      <c r="G19" s="306" t="n"/>
-      <c r="H19" s="306" t="n"/>
-      <c r="I19" s="360">
+      <c r="G19" s="370" t="n"/>
+      <c r="H19" s="370" t="n"/>
+      <c r="I19" s="371">
         <f>IF(OR(G19="",G19=0,H19=""),"",H19/G19)</f>
         <v/>
       </c>
-      <c r="J19" s="230" t="n"/>
-      <c r="K19" s="98" t="n"/>
-      <c r="L19" s="97" t="n"/>
+      <c r="J19" s="372" t="n"/>
+      <c r="K19" s="373" t="n"/>
+      <c r="L19" s="374" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="127">
-      <c r="A20" s="306" t="n">
+      <c r="A20" s="368" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="230" t="inlineStr">
+      <c r="B20" s="369" t="inlineStr">
         <is>
           <t>Inspecciones de seguridad</t>
         </is>
@@ -2888,21 +2939,21 @@
       <c r="D20" s="98" t="n"/>
       <c r="E20" s="98" t="n"/>
       <c r="F20" s="97" t="n"/>
-      <c r="G20" s="306" t="n"/>
-      <c r="H20" s="306" t="n"/>
-      <c r="I20" s="360">
+      <c r="G20" s="370" t="n"/>
+      <c r="H20" s="370" t="n"/>
+      <c r="I20" s="371">
         <f>IF(OR(G20="",G20=0,H20=""),"",H20/G20)</f>
         <v/>
       </c>
-      <c r="J20" s="230" t="n"/>
-      <c r="K20" s="98" t="n"/>
-      <c r="L20" s="97" t="n"/>
+      <c r="J20" s="372" t="n"/>
+      <c r="K20" s="373" t="n"/>
+      <c r="L20" s="374" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="127">
-      <c r="A21" s="306" t="n">
+      <c r="A21" s="368" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="230" t="inlineStr">
+      <c r="B21" s="369" t="inlineStr">
         <is>
           <t>Permisos de trabajo de alto riesgo</t>
         </is>
@@ -2911,21 +2962,21 @@
       <c r="D21" s="98" t="n"/>
       <c r="E21" s="98" t="n"/>
       <c r="F21" s="97" t="n"/>
-      <c r="G21" s="306" t="n"/>
-      <c r="H21" s="306" t="n"/>
-      <c r="I21" s="360">
+      <c r="G21" s="370" t="n"/>
+      <c r="H21" s="370" t="n"/>
+      <c r="I21" s="371">
         <f>IF(OR(G21="",G21=0,H21=""),"",H21/G21)</f>
         <v/>
       </c>
-      <c r="J21" s="230" t="n"/>
-      <c r="K21" s="98" t="n"/>
-      <c r="L21" s="97" t="n"/>
+      <c r="J21" s="372" t="n"/>
+      <c r="K21" s="373" t="n"/>
+      <c r="L21" s="374" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="127">
-      <c r="A22" s="306" t="n">
+      <c r="A22" s="368" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="230" t="inlineStr">
+      <c r="B22" s="369" t="inlineStr">
         <is>
           <t>Análisis de trabajo seguro (ATS)</t>
         </is>
@@ -2934,21 +2985,21 @@
       <c r="D22" s="98" t="n"/>
       <c r="E22" s="98" t="n"/>
       <c r="F22" s="97" t="n"/>
-      <c r="G22" s="306" t="n"/>
-      <c r="H22" s="306" t="n"/>
-      <c r="I22" s="360">
+      <c r="G22" s="370" t="n"/>
+      <c r="H22" s="370" t="n"/>
+      <c r="I22" s="371">
         <f>IF(OR(G22="",G22=0,H22=""),"",H22/G22)</f>
         <v/>
       </c>
-      <c r="J22" s="230" t="n"/>
-      <c r="K22" s="98" t="n"/>
-      <c r="L22" s="97" t="n"/>
+      <c r="J22" s="372" t="n"/>
+      <c r="K22" s="373" t="n"/>
+      <c r="L22" s="374" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="127">
-      <c r="A23" s="306" t="n">
+      <c r="A23" s="368" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="230" t="inlineStr">
+      <c r="B23" s="369" t="inlineStr">
         <is>
           <t>Entregas de EPP</t>
         </is>
@@ -2957,21 +3008,21 @@
       <c r="D23" s="98" t="n"/>
       <c r="E23" s="98" t="n"/>
       <c r="F23" s="97" t="n"/>
-      <c r="G23" s="306" t="n"/>
-      <c r="H23" s="306" t="n"/>
-      <c r="I23" s="360">
+      <c r="G23" s="370" t="n"/>
+      <c r="H23" s="370" t="n"/>
+      <c r="I23" s="371">
         <f>IF(OR(G23="",G23=0,H23=""),"",H23/G23)</f>
         <v/>
       </c>
-      <c r="J23" s="230" t="n"/>
-      <c r="K23" s="98" t="n"/>
-      <c r="L23" s="97" t="n"/>
+      <c r="J23" s="372" t="n"/>
+      <c r="K23" s="373" t="n"/>
+      <c r="L23" s="374" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="127">
-      <c r="A24" s="306" t="n">
+      <c r="A24" s="368" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="230" t="inlineStr">
+      <c r="B24" s="369" t="inlineStr">
         <is>
           <t>Actos y condiciones inseguras reportados (Tarjeta iCAI)</t>
         </is>
@@ -2980,21 +3031,21 @@
       <c r="D24" s="98" t="n"/>
       <c r="E24" s="98" t="n"/>
       <c r="F24" s="97" t="n"/>
-      <c r="G24" s="306" t="n"/>
-      <c r="H24" s="306" t="n"/>
-      <c r="I24" s="360">
+      <c r="G24" s="370" t="n"/>
+      <c r="H24" s="370" t="n"/>
+      <c r="I24" s="371">
         <f>IF(OR(G24="",G24=0,H24=""),"",H24/G24)</f>
         <v/>
       </c>
-      <c r="J24" s="230" t="n"/>
-      <c r="K24" s="98" t="n"/>
-      <c r="L24" s="97" t="n"/>
+      <c r="J24" s="372" t="n"/>
+      <c r="K24" s="373" t="n"/>
+      <c r="L24" s="374" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="127">
-      <c r="A25" s="306" t="n">
+      <c r="A25" s="368" t="n">
         <v>9</v>
       </c>
-      <c r="B25" s="230" t="inlineStr">
+      <c r="B25" s="369" t="inlineStr">
         <is>
           <t>Accidentes de trabajo</t>
         </is>
@@ -3003,21 +3054,21 @@
       <c r="D25" s="98" t="n"/>
       <c r="E25" s="98" t="n"/>
       <c r="F25" s="97" t="n"/>
-      <c r="G25" s="306" t="n"/>
-      <c r="H25" s="306" t="n"/>
-      <c r="I25" s="360">
+      <c r="G25" s="370" t="n"/>
+      <c r="H25" s="370" t="n"/>
+      <c r="I25" s="371">
         <f>IF(OR(G25="",G25=0,H25=""),"",H25/G25)</f>
         <v/>
       </c>
-      <c r="J25" s="230" t="n"/>
-      <c r="K25" s="98" t="n"/>
-      <c r="L25" s="97" t="n"/>
+      <c r="J25" s="372" t="n"/>
+      <c r="K25" s="373" t="n"/>
+      <c r="L25" s="374" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="127">
-      <c r="A26" s="306" t="n">
+      <c r="A26" s="368" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="230" t="inlineStr">
+      <c r="B26" s="369" t="inlineStr">
         <is>
           <t>Incidentes y casi accidentes</t>
         </is>
@@ -3026,15 +3077,15 @@
       <c r="D26" s="98" t="n"/>
       <c r="E26" s="98" t="n"/>
       <c r="F26" s="97" t="n"/>
-      <c r="G26" s="306" t="n"/>
-      <c r="H26" s="306" t="n"/>
-      <c r="I26" s="360">
+      <c r="G26" s="370" t="n"/>
+      <c r="H26" s="370" t="n"/>
+      <c r="I26" s="371">
         <f>IF(OR(G26="",G26=0,H26=""),"",H26/G26)</f>
         <v/>
       </c>
-      <c r="J26" s="230" t="n"/>
-      <c r="K26" s="98" t="n"/>
-      <c r="L26" s="97" t="n"/>
+      <c r="J26" s="372" t="n"/>
+      <c r="K26" s="373" t="n"/>
+      <c r="L26" s="374" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="127">
       <c r="A27" s="137" t="inlineStr">
@@ -3085,18 +3136,18 @@
       <c r="L28" s="348" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1" s="127">
-      <c r="A29" s="69" t="n"/>
-      <c r="B29" s="93" t="n"/>
-      <c r="C29" s="89" t="n"/>
-      <c r="D29" s="69" t="n"/>
-      <c r="E29" s="93" t="n"/>
-      <c r="F29" s="89" t="n"/>
-      <c r="G29" s="69" t="n"/>
-      <c r="H29" s="93" t="n"/>
-      <c r="I29" s="89" t="n"/>
-      <c r="J29" s="69" t="n"/>
-      <c r="K29" s="93" t="n"/>
-      <c r="L29" s="89" t="n"/>
+      <c r="A29" s="367" t="n"/>
+      <c r="B29" s="365" t="n"/>
+      <c r="C29" s="366" t="n"/>
+      <c r="D29" s="367" t="n"/>
+      <c r="E29" s="365" t="n"/>
+      <c r="F29" s="366" t="n"/>
+      <c r="G29" s="367" t="n"/>
+      <c r="H29" s="365" t="n"/>
+      <c r="I29" s="366" t="n"/>
+      <c r="J29" s="367" t="n"/>
+      <c r="K29" s="365" t="n"/>
+      <c r="L29" s="366" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="127">
       <c r="A30" s="137" t="inlineStr">
@@ -3123,16 +3174,16 @@
         </is>
       </c>
       <c r="B31" s="89" t="n"/>
-      <c r="C31" s="100" t="n"/>
-      <c r="D31" s="93" t="n"/>
-      <c r="E31" s="93" t="n"/>
-      <c r="F31" s="93" t="n"/>
-      <c r="G31" s="93" t="n"/>
-      <c r="H31" s="93" t="n"/>
-      <c r="I31" s="93" t="n"/>
-      <c r="J31" s="93" t="n"/>
-      <c r="K31" s="93" t="n"/>
-      <c r="L31" s="89" t="n"/>
+      <c r="C31" s="375" t="n"/>
+      <c r="D31" s="365" t="n"/>
+      <c r="E31" s="365" t="n"/>
+      <c r="F31" s="365" t="n"/>
+      <c r="G31" s="365" t="n"/>
+      <c r="H31" s="365" t="n"/>
+      <c r="I31" s="365" t="n"/>
+      <c r="J31" s="365" t="n"/>
+      <c r="K31" s="365" t="n"/>
+      <c r="L31" s="366" t="n"/>
     </row>
     <row r="32" ht="48" customHeight="1" s="127">
       <c r="A32" s="59" t="inlineStr">
@@ -3141,16 +3192,16 @@
         </is>
       </c>
       <c r="B32" s="89" t="n"/>
-      <c r="C32" s="100" t="n"/>
-      <c r="D32" s="93" t="n"/>
-      <c r="E32" s="93" t="n"/>
-      <c r="F32" s="93" t="n"/>
-      <c r="G32" s="93" t="n"/>
-      <c r="H32" s="93" t="n"/>
-      <c r="I32" s="93" t="n"/>
-      <c r="J32" s="93" t="n"/>
-      <c r="K32" s="93" t="n"/>
-      <c r="L32" s="89" t="n"/>
+      <c r="C32" s="375" t="n"/>
+      <c r="D32" s="365" t="n"/>
+      <c r="E32" s="365" t="n"/>
+      <c r="F32" s="365" t="n"/>
+      <c r="G32" s="365" t="n"/>
+      <c r="H32" s="365" t="n"/>
+      <c r="I32" s="365" t="n"/>
+      <c r="J32" s="365" t="n"/>
+      <c r="K32" s="365" t="n"/>
+      <c r="L32" s="366" t="n"/>
     </row>
     <row r="33" ht="48" customHeight="1" s="127">
       <c r="A33" s="59" t="inlineStr">
@@ -3159,16 +3210,16 @@
         </is>
       </c>
       <c r="B33" s="89" t="n"/>
-      <c r="C33" s="100" t="n"/>
-      <c r="D33" s="93" t="n"/>
-      <c r="E33" s="93" t="n"/>
-      <c r="F33" s="93" t="n"/>
-      <c r="G33" s="93" t="n"/>
-      <c r="H33" s="93" t="n"/>
-      <c r="I33" s="93" t="n"/>
-      <c r="J33" s="93" t="n"/>
-      <c r="K33" s="93" t="n"/>
-      <c r="L33" s="89" t="n"/>
+      <c r="C33" s="375" t="n"/>
+      <c r="D33" s="365" t="n"/>
+      <c r="E33" s="365" t="n"/>
+      <c r="F33" s="365" t="n"/>
+      <c r="G33" s="365" t="n"/>
+      <c r="H33" s="365" t="n"/>
+      <c r="I33" s="365" t="n"/>
+      <c r="J33" s="365" t="n"/>
+      <c r="K33" s="365" t="n"/>
+      <c r="L33" s="366" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="127">
       <c r="A34" s="137" t="inlineStr">
@@ -3221,24 +3272,24 @@
         </is>
       </c>
       <c r="B36" s="97" t="n"/>
-      <c r="C36" s="301" t="n"/>
-      <c r="D36" s="97" t="n"/>
+      <c r="C36" s="372" t="n"/>
+      <c r="D36" s="374" t="n"/>
       <c r="E36" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F36" s="97" t="n"/>
-      <c r="G36" s="301" t="n"/>
-      <c r="H36" s="97" t="n"/>
+      <c r="G36" s="372" t="n"/>
+      <c r="H36" s="374" t="n"/>
       <c r="I36" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J36" s="97" t="n"/>
-      <c r="K36" s="301" t="n"/>
-      <c r="L36" s="97" t="n"/>
+      <c r="K36" s="372" t="n"/>
+      <c r="L36" s="374" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1" s="127">
       <c r="A37" s="302" t="inlineStr">
@@ -3247,24 +3298,24 @@
         </is>
       </c>
       <c r="B37" s="97" t="n"/>
-      <c r="C37" s="301" t="n"/>
-      <c r="D37" s="97" t="n"/>
+      <c r="C37" s="372" t="n"/>
+      <c r="D37" s="374" t="n"/>
       <c r="E37" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F37" s="97" t="n"/>
-      <c r="G37" s="301" t="n"/>
-      <c r="H37" s="97" t="n"/>
+      <c r="G37" s="372" t="n"/>
+      <c r="H37" s="374" t="n"/>
       <c r="I37" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J37" s="97" t="n"/>
-      <c r="K37" s="301" t="n"/>
-      <c r="L37" s="97" t="n"/>
+      <c r="K37" s="372" t="n"/>
+      <c r="L37" s="374" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1" s="127">
       <c r="A38" s="302" t="inlineStr">
@@ -3273,24 +3324,24 @@
         </is>
       </c>
       <c r="B38" s="97" t="n"/>
-      <c r="C38" s="301" t="n"/>
-      <c r="D38" s="97" t="n"/>
+      <c r="C38" s="372" t="n"/>
+      <c r="D38" s="374" t="n"/>
       <c r="E38" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F38" s="97" t="n"/>
-      <c r="G38" s="301" t="n"/>
-      <c r="H38" s="97" t="n"/>
+      <c r="G38" s="372" t="n"/>
+      <c r="H38" s="374" t="n"/>
       <c r="I38" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J38" s="97" t="n"/>
-      <c r="K38" s="301" t="n"/>
-      <c r="L38" s="97" t="n"/>
+      <c r="K38" s="372" t="n"/>
+      <c r="L38" s="374" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
@@ -3304,6 +3355,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="91">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B25:F25"/>
